--- a/RL/results_dnn_film_a.xlsx
+++ b/RL/results_dnn_film_a.xlsx
@@ -566,22 +566,22 @@
         <v>73.95</v>
       </c>
       <c r="H2" t="n">
-        <v>5259</v>
+        <v>4009</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.01</v>
+        <v>19.95</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>5008</v>
+        <v>4009</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -590,22 +590,22 @@
         <v>73.95</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>83.5</v>
+        <v>134.5</v>
       </c>
       <c r="V2" t="n">
         <v>166.05</v>
@@ -636,7 +636,7 @@
         <v>41.77</v>
       </c>
       <c r="H3" t="n">
-        <v>38258</v>
+        <v>36009</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -645,13 +645,13 @@
         <v>41.77</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>38258</v>
+        <v>36009</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -660,22 +660,22 @@
         <v>41.77</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>190.3</v>
+        <v>191.9</v>
       </c>
       <c r="V3" t="n">
         <v>198.23</v>
@@ -706,22 +706,22 @@
         <v>73.95</v>
       </c>
       <c r="H4" t="n">
-        <v>5259</v>
+        <v>4009</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>75.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.01</v>
+        <v>19.95</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5008</v>
+        <v>4009</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -730,22 +730,22 @@
         <v>73.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>50.8</v>
+        <v>65</v>
       </c>
       <c r="V4" t="n">
         <v>166.05</v>
@@ -776,7 +776,7 @@
         <v>41.77</v>
       </c>
       <c r="H5" t="n">
-        <v>38258</v>
+        <v>36009</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>41.77</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>38258</v>
+        <v>36009</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -800,22 +800,22 @@
         <v>41.77</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>161.2</v>
+        <v>201.2</v>
       </c>
       <c r="V5" t="n">
         <v>198.23</v>
@@ -885,7 +885,7 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>50.5</v>
+        <v>52.1</v>
       </c>
       <c r="V6" t="n">
         <v>226.05</v>
@@ -916,7 +916,7 @@
         <v>41.77</v>
       </c>
       <c r="H7" t="n">
-        <v>38258</v>
+        <v>36009</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>41.77</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>38258</v>
+        <v>36009</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -940,22 +940,22 @@
         <v>41.77</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>166.4</v>
+        <v>218.2</v>
       </c>
       <c r="V7" t="n">
         <v>258.23</v>
@@ -986,22 +986,22 @@
         <v>73.95</v>
       </c>
       <c r="H8" t="n">
-        <v>5259</v>
+        <v>4009</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>75.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.01</v>
+        <v>19.95</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>5008</v>
+        <v>4009</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1010,22 +1010,22 @@
         <v>73.95</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>56.8</v>
+        <v>60</v>
       </c>
       <c r="V8" t="n">
         <v>226.05</v>
@@ -1095,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>168.4</v>
+        <v>190.9</v>
       </c>
       <c r="V9" t="n">
         <v>258.23</v>
@@ -1126,7 +1126,7 @@
         <v>73.95</v>
       </c>
       <c r="H10" t="n">
-        <v>5008</v>
+        <v>4009</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         <v>73.95</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5008</v>
+        <v>4009</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1150,22 +1150,22 @@
         <v>73.95</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>60.6</v>
+        <v>50.9</v>
       </c>
       <c r="V10" t="n">
         <v>999926.05</v>
@@ -1235,7 +1235,7 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>187.2</v>
+        <v>179.6</v>
       </c>
       <c r="V11" t="n">
         <v>999958.23</v>
@@ -1266,22 +1266,22 @@
         <v>73.95</v>
       </c>
       <c r="H12" t="n">
-        <v>5259</v>
+        <v>4009</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>75.15000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.01</v>
+        <v>19.95</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5008</v>
+        <v>4009</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1290,22 +1290,22 @@
         <v>73.95</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>19.95</v>
       </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
       <c r="R12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>50.9</v>
+        <v>56.7</v>
       </c>
       <c r="V12" t="n">
         <v>999926.05</v>
@@ -1375,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>166</v>
+        <v>182.6</v>
       </c>
       <c r="V13" t="n">
         <v>999958.23</v>
@@ -1445,19 +1445,19 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>-2.5</v>
+        <v>12.92</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>12.92</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>182.14</v>
@@ -1471,19 +1471,19 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>5.2</v>
+        <v>12.92</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6.46</v>
+        <v>12.92</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>242.14</v>
@@ -1497,19 +1497,19 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1.69</v>
+        <v>12.92</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2.94</v>
+        <v>12.92</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>999942.14</v>
